--- a/backtest_runs/20260410_193731/by_symbol/SYM/SYM.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/SYM/SYM.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-5544.550000000007</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>99596.75999999999</v>
@@ -679,7 +679,7 @@
         <v>-10081</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>89515.75999999999</v>
@@ -863,7 +863,7 @@
         <v>-1814.579999999997</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>96673.27</v>
@@ -909,7 +909,7 @@
         <v>-1008.100000000014</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>95665.16999999998</v>
@@ -1185,7 +1185,7 @@
         <v>-2016.199999999993</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>100201.62</v>
@@ -1231,7 +1231,7 @@
         <v>-6250.22000000001</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>93951.39999999998</v>
@@ -1277,7 +1277,7 @@
         <v>-3225.919999999985</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>90725.48</v>
@@ -1415,7 +1415,7 @@
         <v>-2923.489999999992</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100907.29</v>
@@ -1461,7 +1461,7 @@
         <v>-1915.390000000013</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>98991.89999999998</v>
@@ -1553,7 +1553,7 @@
         <v>-705.6700000000029</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>101512.15</v>
@@ -1645,7 +1645,7 @@
         <v>-3427.539999999999</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>108367.23</v>
